--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,248 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125194877</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Kroksjöinfarten a16700, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>569425</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6433040</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125195712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569379</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433060</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194877</v>
+        <v>125195712</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,19 +836,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569425</v>
+        <v>569379</v>
       </c>
       <c r="R3" t="n">
-        <v>6433040</v>
+        <v>6433060</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125195712</v>
+        <v>125194877</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569379</v>
+        <v>569425</v>
       </c>
       <c r="R4" t="n">
-        <v>6433060</v>
+        <v>6433040</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125195712</v>
+        <v>125194877</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,19 +836,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569379</v>
+        <v>569425</v>
       </c>
       <c r="R3" t="n">
-        <v>6433060</v>
+        <v>6433040</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194877</v>
+        <v>125195712</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569425</v>
+        <v>569379</v>
       </c>
       <c r="R4" t="n">
-        <v>6433040</v>
+        <v>6433060</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125195712</v>
+        <v>125194877</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,19 +836,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569379</v>
+        <v>569425</v>
       </c>
       <c r="R3" t="n">
-        <v>6433060</v>
+        <v>6433040</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194877</v>
+        <v>125195712</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>58001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569425</v>
+        <v>569379</v>
       </c>
       <c r="R4" t="n">
-        <v>6433040</v>
+        <v>6433060</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>125194877</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,12 +915,7 @@
         <v>125195712</v>
       </c>
       <c r="B4" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16700-2025 artfynd.xlsx
+++ b/artfynd/A 16700-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122859676</v>
+        <v>125194877</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,19 +710,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten, Sm</t>
+          <t>Norra Kroksjöinfarten a16700, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569383</v>
+        <v>569425</v>
       </c>
       <c r="R2" t="n">
-        <v>6433052</v>
+        <v>6433040</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,27 +791,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194877</v>
+        <v>122859676</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,19 +826,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Kroksjöinfarten a16700, Sm</t>
+          <t>Norra Kroksjöinfarten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569425</v>
+        <v>569383</v>
       </c>
       <c r="R3" t="n">
-        <v>6433040</v>
+        <v>6433052</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +910,7 @@
         <v>125195712</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
